--- a/AAII_Financials/Yearly/MTHRY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTHRY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>MTHRY</t>
   </si>
@@ -656,147 +656,159 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44286</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43921</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43555</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43190</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2209800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1902500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1579300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1736300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1714200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1529800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1217200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1020300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>889500</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1103900</v>
+      </c>
+      <c r="E9" s="3">
         <v>871700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>650200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>719400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>699100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>594900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>539800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>444100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>383400</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1105900</v>
+      </c>
+      <c r="E10" s="3">
         <v>1030800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>929100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1016900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1015100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>934900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>677400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>576100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>506100</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -809,8 +821,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -826,21 +839,24 @@
       <c r="G12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="3">
         <v>400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>100</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>400</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -868,69 +884,78 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E14" s="3">
         <v>11800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>17300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-248800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-26800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-24900</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>90900</v>
+      </c>
+      <c r="E15" s="3">
         <v>70600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>48600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>44000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>40600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>37400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>29100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>6900</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -940,68 +965,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1765200</v>
+      </c>
+      <c r="E17" s="3">
         <v>1488100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1145400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1206600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1159400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>997800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>897000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>769400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>635000</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>444500</v>
+      </c>
+      <c r="E18" s="3">
         <v>414500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>434000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>529700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>554700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>532000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>320200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>250900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>254600</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1014,82 +1046,89 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-23900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-17700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-29500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-20800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>15800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>800</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>559300</v>
+      </c>
+      <c r="E21" s="3">
         <v>502800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>512100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>594500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>579500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>568500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>349200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>260700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>261300</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E22" s="3">
         <v>4600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>400</v>
       </c>
       <c r="H22" s="3">
         <v>400</v>
@@ -1097,75 +1136,84 @@
       <c r="I22" s="3">
         <v>400</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
+      <c r="J22" s="3">
+        <v>400</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>479700</v>
+      </c>
+      <c r="E23" s="3">
         <v>432600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>455100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>559100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>792100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>526800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>321600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>279200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>279600</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>139800</v>
+      </c>
+      <c r="E24" s="3">
         <v>136500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>134200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>168000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>247700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>154300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>97200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>86600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>84000</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1193,69 +1241,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>339900</v>
+      </c>
+      <c r="E26" s="3">
         <v>296100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>321000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>391000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>544400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>372500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>224500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>192600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>195700</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>308800</v>
+      </c>
+      <c r="E27" s="3">
         <v>270400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>299300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>368800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>525800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>342000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>201100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>176700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>185300</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1283,9 +1340,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1313,9 +1373,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1343,9 +1406,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1373,69 +1439,78 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E32" s="3">
         <v>17700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>29500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>20800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-15800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-800</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>308800</v>
+      </c>
+      <c r="E33" s="3">
         <v>270300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>299300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>368800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>525800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>342000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>201100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>176700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>185300</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1463,74 +1538,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>308800</v>
+      </c>
+      <c r="E35" s="3">
         <v>270300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>299300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>368800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>525800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>342000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>201100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>176700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>185300</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44286</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43921</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43555</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43190</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1543,8 +1627,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1557,38 +1642,42 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>982200</v>
+      </c>
+      <c r="E41" s="3">
         <v>901100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>989500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>890100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>858500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>806000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>445600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>248500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>223500</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1616,39 +1705,45 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>469300</v>
+      </c>
+      <c r="E43" s="3">
         <v>434400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>343300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>380200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>419000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>394900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>312400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>255500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>234500</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1676,159 +1771,177 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>236100</v>
+      </c>
+      <c r="E45" s="3">
         <v>260700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>234700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>239600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>341900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>263200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>355700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>59400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>34600</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1717100</v>
+      </c>
+      <c r="E46" s="3">
         <v>1625600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1591600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1530600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1637700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1483800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1129600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>577400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>504600</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>496100</v>
+      </c>
+      <c r="E47" s="3">
         <v>503600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>469300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>478900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>407900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>156100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>147500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>121200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>80800</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>346800</v>
+      </c>
+      <c r="E48" s="3">
         <v>324600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>174800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>143200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>103300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>110300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>90800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14600</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1404300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1379100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>972400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>842900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>682700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>686000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>663200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>513200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>478100</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1856,9 +1969,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1886,14 +2002,17 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>8</v>
@@ -1901,24 +2020,27 @@
       <c r="F52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G52" s="3">
-        <v>0</v>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H52" s="3">
         <v>0</v>
       </c>
-      <c r="I52" s="3" t="s">
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3" t="s">
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1946,39 +2068,45 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>4008700</v>
+      </c>
+      <c r="E54" s="3">
         <v>3884800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3244700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3013900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2849100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2469500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2061700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1239100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1096400</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1991,8 +2119,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2005,188 +2134,207 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>365200</v>
+      </c>
+      <c r="E57" s="3">
         <v>333500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>257000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>247200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>238600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>185900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>160700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>131000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>118900</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>66300</v>
+      </c>
+      <c r="E58" s="3">
         <v>54400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>36100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>24600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>24100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>32500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>23800</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>172300</v>
+      </c>
+      <c r="E59" s="3">
         <v>136900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>131900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>158300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>189900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>216900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>152800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>107500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>98900</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>629000</v>
+      </c>
+      <c r="E60" s="3">
         <v>548300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>444100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>448200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>471200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>454900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>354500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>252700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>231200</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>314200</v>
+      </c>
+      <c r="E61" s="3">
         <v>288900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>174000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>53500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>44200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>49000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>32800</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E62" s="3">
         <v>34600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>45500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>35300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>23400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>21300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>12300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>13500</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2214,9 +2362,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2244,9 +2395,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2274,39 +2428,45 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1199600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1128200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>820300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>685500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>675500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>595500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>466900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>316100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>294500</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2319,8 +2479,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2348,9 +2509,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2378,9 +2542,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2408,9 +2575,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2438,39 +2608,45 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2043000</v>
+      </c>
+      <c r="E72" s="3">
         <v>1935600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1742600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1739300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1588600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1240100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>978100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>794400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>678400</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2498,9 +2674,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2528,9 +2707,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2558,39 +2740,45 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2567300</v>
+      </c>
+      <c r="E76" s="3">
         <v>2527200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>2326600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>2276500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2123300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1806600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1543800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>891000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>776600</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2618,74 +2806,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44286</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43921</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43555</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43190</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>308800</v>
+      </c>
+      <c r="E81" s="3">
         <v>270300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>299300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>368800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>525800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>342000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>201100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>176700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>185300</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2698,38 +2895,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>108400</v>
+      </c>
+      <c r="E83" s="3">
         <v>81500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>58700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>55900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>51700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>51900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>41800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>10900</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2757,9 +2958,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2787,9 +2991,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2817,9 +3024,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2847,9 +3057,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2877,39 +3090,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>441900</v>
+      </c>
+      <c r="E89" s="3">
         <v>345500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>385500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>429600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>429100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>421600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>249000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>160200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>149800</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2922,38 +3141,42 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-48300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-42000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-35800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-44500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-17200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-13000</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2981,9 +3204,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3011,39 +3237,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-99900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-261400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-260900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-165000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-192800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>32500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-463600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-79300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-68600</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3056,38 +3288,42 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>89700</v>
+      </c>
+      <c r="E96" s="3">
         <v>95200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>85300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>81700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>67100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>52200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>42100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>30300</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3115,9 +3351,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3145,9 +3384,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3175,97 +3417,109 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-223100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-181400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>62400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-171800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-134800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-105000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>403300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-45200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-44800</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>14700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>20200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>13000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>22900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>23400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-2200</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>133600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-98400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>207200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>105800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>124400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>372500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>189700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>34400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>34200</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
